--- a/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
@@ -572,7 +572,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0</v>

--- a/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
@@ -9,13 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NF-e entradas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT-e" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NF-e itens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT-e" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NF-e entradas'!$A$4:$T$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CT-e'!$A$4:$Q$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NFS-e'!$A$4:$Z$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NF-e itens'!$A$4:$T$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CT-e'!$A$4:$Q$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'NFS-e'!$A$4:$Z$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -641,6 +643,36 @@
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>NF-e itens</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Relatorio_Detalhamento_Produtos.xlsx (item a item, 25 campos)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4669,6 +4701,6566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:T86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NF-e itens</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Item a item, XML x Detalhamento de Produtos: CFOP, NCM, CEST, origem, CST, quantidade, valores, bases, alíquotas, ICMS, ST, IPI, PIS e COFINS (25 campos). Valores mostrados = XML; a coluna Resultado lista cada campo que difere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Produto (XML)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Orig/CST</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Qtd</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Valor produto</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Base ICMS</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>% ICMS</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>ICMS-ST</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>CST IPI</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>CST PIS/COF</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>Chave</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Lunaflexo Tecnologia Adesiva Eireli</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Rotulos Adesivos - Creme Relaxante Afro Nature (Contra Rotulo). 65x160mm, 2x0 cores, Tinta UV Pantone em Bopp Fosco 20G</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>39191090</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2740</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>41260906015875000143550010000037951000701710</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Lunaflexo Tecnologia Adesiva Eireli</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Rotulos Adesivos - Etiq. 20MM (Numero 1,2,3). 20x20mm, 2x0 cores, Tinta UV Pantone em Bopp Fosco 20G Borracha.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>39191090</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>41260906015875000143550010000037951000701710</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>41731</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ALCOOL ETILICO 99 - ONU 1170 ETANOL (ALCOOL ETILICO) 3 GE II BOMBONA DIPANOL 99</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>22071010</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>0/51</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>1870</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>1870</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>224.41</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>125.06</v>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>41260904993269000177550010000417311010503945</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>THERMOSUL RESISTENCIAS ELETRICAS LTDA</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>RESIST. MICA EM U D85X105X85X110MM 800WX220V C/8 FUROS D8MM CABO 200MM</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>85334099</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1296</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>41260966434370000145550010000003001634619321</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>THERMOSUL RESISTENCIAS ELETRICAS LTDA</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>RESIST. COL. EM U 80X105X80X109MM 800WX220V CABO 200MM C/8 FUROS D14MM 1 FURO D15 CABO 200MM</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>85334099</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1296</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>41260966434370000145550010000003001634619321</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>695</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>REATEC DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ETANOLAMINA MONO PS 1000ml  (2-Aminoetanol) REATEC</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>29221100</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>3738</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>41260962341566000134550010000006951857187453</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Cliche Personalizado</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>466.98</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Rotulo Cosmetici - Oleo Vegetal Cartamo 50ml - 40x100 mm - Bopp Metalizado - Lam.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>968</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Rotulo Cosmetici - Oleo Vegetal Chia 50ml - 40x100 mm - Bopp Metalizado - Lam.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4475</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>984.5</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Rotulo Cosmetici - Oleo Vegetal Girassol 50ml - 40x100 mm - Bopp Metalizado - Lam.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>4420</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>972.4</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Cliche Personalizado</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>542.39</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>786</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Rotulo Cosmetici Desperta Cachos 300ml- 155x140 mm - Bopp Metalizado - Lam. Fosca.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>5620</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>3068.52</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007861702940405</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>5027</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>ETIQUETAS - 3,5 X 1,3 CM, LOTE 166955-25075</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>5923</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000050271834583570</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>22837</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>CARBON CIENTIFICA LTDA</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SULFITO DE SODIO ANIDRO PA 1000G - CARBON</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>28321010</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>41260944114040000130550010000228371000945488</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>22837</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>CARBON CIENTIFICA LTDA</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>PIROFOSFATO DE SODIO (TETRABASICO) DECAHIDRATADO PA 1000G - CARBON</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>28353920</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>41260944114040000130550010000228371000945488</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Agar Triptico de soja (TSA) pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>250.39</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>250.39</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Agar Sabouraud Dextrose pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>222.56</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>222.56</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Agar PCA pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Agar Mac Conkey pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R23" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Agar Cetrimide pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>226.01</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>226.01</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Agar Baird Parker pcte c/ 10 placas 90x15mm</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>317.89</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>317.89</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Acquaplus I sachê c/ 10 testes</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>915.08</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>915.08</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>178.44</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>160326</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Caldo BHI cx c/ 10 tubos</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>38221990</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>246.51</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>246.51</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>41260973636391000109550010001603261915612489</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>4920</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>DISPOLI COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>LUVA DESCARTAVEL PLASTICA POLI C/100 UN</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>39262000</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>169.38</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>41260941726398000125550010000049201009949200</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>5048</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>CARTUCHO COLA FUNDO AUTOMATICO - NATURA COLOR 60G - 367X30X160CM (CLA)</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>5923</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>1964</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000050481113690367</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>2564</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>AGATHA INDUSTRIA DE MANUFATURADOS LTDA</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>PINCEL TAM G PROFISSIONAL</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>96033000</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>0/201</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>924</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>43260954079636000108550010000025641087230517</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>795</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Rotulo Cosmetici Afronature Neutralizante - 211x127 mm - Bopp Transparente - Pantone</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>12550</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>3890.5</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007951158784741</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>795</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Cliche Personalizado</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>216.39</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007951158784741</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>5080</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>CAIXA - MODELO NATURA COLOR 60G - 1 MODELOS - 14,8X23CM</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>5670</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000050801135229929</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>5133</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ROTULO 03 MODELOS</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>2136</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000051331151580428</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>8099</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>VALVULA MIST SPRAYER 24/410 PRATA</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>84248990</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>1408.12</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>35260939237959000180550010000080991000082318</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>8112</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>OUTLET PREMIUM PACK LTDA</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>FRASCO ELEGANCE 60ML 24/410 RUBI LAPIDADO 2MB TAMPA SAN S DEC</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>1064.12</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>35260934970658000148550010000081121000087609</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>8112</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>OUTLET PREMIUM PACK LTDA</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SOBRETAMPA ELEGANCE PETG 60/100/120ML RUBI LAPIDADO 3MB S DEC</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>39235000</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>1397.91</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>35260934970658000148550010000081121000087609</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>13721</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>CAETANO PLASTICOS EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>SACOS PLASTICOS 18X30X0,10 C/1000 UNID.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>39232110</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="6" t="inlineStr"/>
+      <c r="O38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>41260937295717000118550010000137211931581334</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>13721</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>CAETANO PLASTICOS EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SACOS PLASTICOS 40X60X0,10 C/1000 UNID.</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>39232190</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>224.64</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="6" t="inlineStr"/>
+      <c r="O39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>41260937295717000118550010000137211931581334</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>13721</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>CAETANO PLASTICOS EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SACOS PLASTICOS 60X100X0,10 C/1000 UNID.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>39232190</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>561.6</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>41260937295717000118550010000137211931581334</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>13721</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>CAETANO PLASTICOS EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>SACOS PLASTICOS 90X120X0,10 C/100 UNID.</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>39232190</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>1450.02</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>41260937295717000118550010000137211931581334</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>5162</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>ROTULOS - 11X8,5CM - 3 MODELOS</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>5923</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>1112</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000051621201311907</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>ILS TECNOLOGIA EM EQUIP DE SEG DO TRABALHO LTDA</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>BOTINA BRACOL USAFE BIDENSIDADE BICO PVC NR 41 CA - 48413</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>64039190</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>41260910265455000192550010000404511000405060</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>ILS TECNOLOGIA EM EQUIP DE SEG DO TRABALHO LTDA</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>BOTA PVC PRETA WORKFLEX C/FORRO C/MEDIO N 40 - CA 37154</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>64019200</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>41260910265455000192550010000404511000405060</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>ILS TECNOLOGIA EM EQUIP DE SEG DO TRABALHO LTDA</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>SAPATO FLEX CLEAN MARLUVAS PRETO EM EVA TAM 40 CA48714</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>64019990</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>110.62</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>41260910265455000192550010000404511000405060</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>ILS TECNOLOGIA EM EQUIP DE SEG DO TRABALHO LTDA</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>JALECO TNT KAMICON BRANCO M/LONGA C/BOTAO C/ELAST PCT C/10</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>56031190</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>41260910265455000192550010000404511000405060</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>418</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>SAVATEC COMERCIO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>SOLUÇÃO DE LIMPEZA 1000Q</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>38140090</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>0/103</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>41260959087034000108550010000004181258202600</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>418</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>SAVATEC COMERCIO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>MAKE UP 7050TP</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>38140090</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>0/103</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>959.6799999999999</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>41260959087034000108550010000004181258202600</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>5170</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>ADESIVO - 18X15,5CM - 2 MODELOS, LOTE 167070-25212</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>667.2</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000051701177572396</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>814</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Etiqueta Balanca - 40x40 mm - Couche Termico - RL 30 Mts Dupla</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000008141610067850</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>6782</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>PANO ROLO MULTIUSO BRANCO 28x240 INOVEN</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>56039240</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>1/00</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>799</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>799</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6" t="inlineStr"/>
+      <c r="O51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q51" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="R51" s="8" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>41260949547438000183550010000067821963905200</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>6782</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>CABO ALUMINIO S ROSCA NOBRE 22MM X 1,40M</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>76082090</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="6" t="inlineStr"/>
+      <c r="O52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q52" s="8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R52" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>41260949547438000183550010000067821963905200</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>23127</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>CARBON CIENTIFICA LTDA</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>MONOETANOLAMINA PA 1000ML - CARBON lote 11622</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>29221100</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T53" s="6" t="inlineStr">
+        <is>
+          <t>41260944114040000130550010000231271000948452</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>30338</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>ALTEC IND.COM.IMP.E EXP.LTDA.</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TAMPA ALUM.20MM RV PRATA 320580</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>83099000</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>2506.56</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>2506.56</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>300.79</v>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="inlineStr"/>
+      <c r="O54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="R54" s="8" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T54" s="6" t="inlineStr">
+        <is>
+          <t>35260967598292000187550010000303381000323387</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Sul Tape Comercio de Embalagens EIRELI</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>FILME STRETCH CORELESS 500 X 25 M</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>39201099</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>0/103</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T55" s="6" t="inlineStr">
+        <is>
+          <t>41260925141658000144550020000032141236266620</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Sul Tape Comercio de Embalagens EIRELI</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>PLASTICO BOLHA 1,20 MM PRO</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>39239090</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>0/103</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T56" s="6" t="inlineStr">
+        <is>
+          <t>41260925141658000144550020000032141236266620</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>17187</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>ONIXSUL COSMETICOS</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>...CDC60 - CARTUCHO COLORACAO DIVINE COLORS 60G</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>39239090</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>0/400</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>5700</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T57" s="6" t="inlineStr">
+        <is>
+          <t>41260918074269000188550010000171871932036922</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>PUMP 28/410 BRANCA PESCANTE 230MM</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>84132000</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>1/500</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="inlineStr"/>
+      <c r="O58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T58" s="6" t="inlineStr">
+        <is>
+          <t>41260921822008000103550020000045511028307079</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>PUMP PROFISSIONAL 28/410 NATURAL PRESCANTE 270MM</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>84132000</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>1/500</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="6" t="inlineStr"/>
+      <c r="O59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T59" s="6" t="inlineStr">
+        <is>
+          <t>41260921822008000103550020000045511028307079</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>MINI GATILHO 24/410 PRETO PESCANTE 250MM</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>84248990</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>0/500</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T60" s="6" t="inlineStr">
+        <is>
+          <t>41260921822008000103550020000045511028307079</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>MINI GATILHO 24/410 NATURAL PESCANTE 250MM</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>84248990</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>0/500</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T61" s="6" t="inlineStr">
+        <is>
+          <t>41260921822008000103550020000045511028307079</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>4551</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>PUMP 28/410 PRETA PESCANTE 230MM</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>84132000</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>1/500</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="6" t="inlineStr"/>
+      <c r="O62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="Q62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 99 sem valor (o relatório não traz esse grupo); COFINS CST 99 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T62" s="6" t="inlineStr">
+        <is>
+          <t>41260921822008000103550020000045511028307079</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>5233</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>CAIXA - NATURE COLOR 60G (FUNDO AUTOMÁTICO) - 15,5X23,2CM</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>2420.01</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T63" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000052331135756040</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>5235</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>CAIXA - NATURE COLOR 60G - ABERTA 14,8X23CM</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>49111090</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>1760</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T64" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000052351191452986</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>55874</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Mix Perfumaria</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Frasco Impresso Ox 30v 900ml - Eternize</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="I65" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="J65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>41260906237330000181550010000558741118273450</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>117690</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>BISPHARMA EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>COLORACAO HIDRATANTE PROFISSIONAL 60G Item.Ped.:       OP:119087 Cod.Externo:345566</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>76121000</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="I66" s="8" t="n">
+        <v>24897.18</v>
+      </c>
+      <c r="J66" s="8" t="n">
+        <v>24897.18</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L66" s="8" t="n">
+        <v>2987.66</v>
+      </c>
+      <c r="M66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O66" s="8" t="n">
+        <v>1618.32</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q66" s="8" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="R66" s="8" t="n">
+        <v>1665.12</v>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T66" s="6" t="inlineStr">
+        <is>
+          <t>35260959610485000188550050001176901971337303</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>275966</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>TRANSCUTOL CG - TB 25 KG</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>29094429</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>1/00</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>3873.74</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>3873.74</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L67" s="8" t="n">
+        <v>154.95</v>
+      </c>
+      <c r="M67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="R67" s="8" t="n">
+        <v>282.63</v>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T67" s="6" t="inlineStr">
+        <is>
+          <t>35260949698723003110550550002759661838341135</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>14838</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Mix Cosmeticos Ltda</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Frasco Impresso Ox 20v 900ml- Eternize</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>632</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>948</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="6" t="inlineStr"/>
+      <c r="O68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T68" s="6" t="inlineStr">
+        <is>
+          <t>50260927697083000176550010000148381118293998</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>48241</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>HS INKLASER LTDA</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>CARTUCHO BLK 13 PRETO</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>84439923</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>6/00</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>983</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>1042.55</v>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L69" s="8" t="n">
+        <v>125.11</v>
+      </c>
+      <c r="M69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="R69" s="8" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T69" s="6" t="inlineStr">
+        <is>
+          <t>35260918858535000163550010000482411465753374</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>55913</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Mix Perfumaria</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Frasco Impresso Ox 20v 900ml- Eternize</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>371</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="6" t="inlineStr"/>
+      <c r="O70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T70" s="6" t="inlineStr">
+        <is>
+          <t>41260906237330000181550010000559131118294105</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>141811</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>CASHMERE - 204510</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>33029019</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>4644.06</v>
+      </c>
+      <c r="J71" s="8" t="n">
+        <v>4644.06</v>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L71" s="8" t="n">
+        <v>557.29</v>
+      </c>
+      <c r="M71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="n">
+        <v>150.93</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="R71" s="8" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>35260962514971000107550010001418111026832844</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>391</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>CHEMYUNION LTDA</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Antecipação de Pagamento (Adiantamento)</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>8472.040000000001</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="6" t="inlineStr"/>
+      <c r="O72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr"/>
+      <c r="Q72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T72" s="6" t="inlineStr">
+        <is>
+          <t>31260958309709000820550070000003911550019201</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>392</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>CHEMYUNION LTDA</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Antecipação de Pagamento (Adiantamento)</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>275.34</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="6" t="inlineStr"/>
+      <c r="O73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr"/>
+      <c r="Q73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T73" s="6" t="inlineStr">
+        <is>
+          <t>31260958309709000820550070000003921611175930</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>5382</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>RÓTULOS FLEXO DIGITAL - 13 X 7,5 CM</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>48211000</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>0/41</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T74" s="6" t="inlineStr">
+        <is>
+          <t>41260903839251000152550030000053821102007626</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>14856</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Mix Cosmeticos Ltda</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Frasco Impresso Ox 30v 900ml - Eternize</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="6" t="inlineStr"/>
+      <c r="O75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T75" s="6" t="inlineStr">
+        <is>
+          <t>50260927697083000176550010000148561118323143</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>19303</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>CHEMYUNION LTDA</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Uniox C (20,000)</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>34024200</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>5/00</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>8472.040000000001</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>8472.040000000001</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>1016.64</v>
+      </c>
+      <c r="M76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="n">
+        <v>275.34</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q76" s="8" t="n">
+        <v>123.01</v>
+      </c>
+      <c r="R76" s="8" t="n">
+        <v>566.61</v>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T76" s="6" t="inlineStr">
+        <is>
+          <t>31260958309709000820550020000193031662295529</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>42285</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>KERANUTRI</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>38249989</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>1/00</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>4017.69</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>4017.69</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>160.71</v>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="n">
+        <v>261.15</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="R77" s="8" t="n">
+        <v>115.71</v>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T77" s="6" t="inlineStr">
+        <is>
+          <t>35260911340087000162550010000422851305252223</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>56004</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Mix Perfumaria</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Frasco Impresso Ox 30v 900ml - Eternize</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>39233090</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>0/90</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="6" t="inlineStr"/>
+      <c r="O78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Q78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>OK (PIS CST 49 sem valor (o relatório não traz esse grupo); COFINS CST 49 sem valor (o relatório não traz esse grupo))</t>
+        </is>
+      </c>
+      <c r="T78" s="6" t="inlineStr">
+        <is>
+          <t>41260906237330000181550010000560041118322920</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>222098</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>FARMANILQUIMA COM. ANILINAS E PRODS.QUIM.LTDA</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>OLEO DE CAMOMILA 100 ML</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>15159090</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>0/102</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T79" s="6" t="inlineStr">
+        <is>
+          <t>41260976509488000149550010002220981017634246</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>MERCKPAR COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>SULFITO DE SODIO ANIDRO PA 1000g REATEC</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>28321010</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>0/101</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="6" t="inlineStr"/>
+      <c r="O80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>41260963460684000124550010000000421742919846</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>38175</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>ALLOXY ESPECIALIDADES QUIMICAS LTDA</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>IX 351 IBC</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>28470000</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>0/51</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>5593.5</v>
+      </c>
+      <c r="J81" s="8" t="n">
+        <v>5593.5</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L81" s="8" t="n">
+        <v>671.22</v>
+      </c>
+      <c r="M81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="R81" s="8" t="n">
+        <v>374.09</v>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="inlineStr">
+        <is>
+          <t>41260916987597000140550010000381751288422874</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>97145</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado Boza Ltda</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Cha Mate Mandiervas Natural Cx 40g</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>09030090</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>0/40</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R82" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>41260973419905000174550010000971451002693820</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>97145</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado Boza Ltda</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Filtro Papel Cafe Brigitta 103 C/30un</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>48232099</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>0/00</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L83" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R83" s="8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T83" s="6" t="inlineStr">
+        <is>
+          <t>41260973419905000174550010000971451002693820</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>97145</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado Boza Ltda</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Cafe 3 Coracoes Extra Forte Vacuo 500g</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>09012100</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>0/40</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="J84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T84" s="6" t="inlineStr">
+        <is>
+          <t>41260973419905000174550010000971451002693820</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>97145</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado Boza Ltda</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Acucar Alto Alegre Refinado 1kg</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>17019900</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>0/40</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="J85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="inlineStr">
+        <is>
+          <t>41260973419905000174550010000971451002693820</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I86" s="13">
+        <f>SUM(I5:I85)</f>
+        <v/>
+      </c>
+      <c r="J86" s="13">
+        <f>SUM(J5:J85)</f>
+        <v/>
+      </c>
+      <c r="L86" s="13">
+        <f>SUM(L5:L85)</f>
+        <v/>
+      </c>
+      <c r="M86" s="13">
+        <f>SUM(M5:M85)</f>
+        <v/>
+      </c>
+      <c r="O86" s="13">
+        <f>SUM(O5:O85)</f>
+        <v/>
+      </c>
+      <c r="Q86" s="13">
+        <f>SUM(Q5:Q85)</f>
+        <v/>
+      </c>
+      <c r="R86" s="13">
+        <f>SUM(R5:R85)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T85"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8916,7 +15508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9190,7 +15782,7 @@
       </c>
       <c r="Y5" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z5" s="6" t="inlineStr">
@@ -9386,7 +15978,7 @@
       </c>
       <c r="Y7" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z7" s="6" t="inlineStr">
@@ -9586,7 +16178,7 @@
       </c>
       <c r="Y9" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z9" s="6" t="inlineStr">
@@ -9786,7 +16378,7 @@
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -10186,7 +16778,7 @@
       </c>
       <c r="Y15" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z15" s="6" t="inlineStr">
@@ -10486,7 +17078,7 @@
       </c>
       <c r="Y18" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z18" s="6" t="inlineStr">
@@ -10586,7 +17178,7 @@
       </c>
       <c r="Y19" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK (XML sem base do ISS - Simples, sem retenção; o relatório repete o valor)</t>
         </is>
       </c>
       <c r="Z19" s="6" t="inlineStr">

--- a/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Cruzamento_Entradas_Relatorios_x_XML_09-2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NF-e entradas'!$A$4:$T$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'NF-e itens'!$A$4:$T$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CT-e'!$A$4:$Q$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CT-e'!$A$4:$Q$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'NFS-e'!$A$4:$Z$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -11261,7 +11261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11293,7 +11293,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>XML x Relatorio_CTe (SIEG) - todos os CT-e em que a Cosmetici aparece. Amarelo = Cosmetici tomadora sem XML; cinza = tomador é outra empresa ou cancelado.</t>
+          <t>XML x Relatorio_CTe (SIEG) - só os CT-e em que a Cosmetici é TOMADORA (os de outros tomadores não são escriturados e ficam fora). Amarelo = sem XML na pasta (pedir); cinza = cancelado.</t>
         </is>
       </c>
     </row>
@@ -11386,44 +11386,44 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>2043498</v>
+        <v>4683984</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+          <t>RODONAVES TRANSPORTES E ENCOMENDAS LTDA</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>00428307002301</t>
+          <t>44914992003820</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>PR-SC</t>
+          <t>PR-SP</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>tomador 09344397000103</t>
+          <t>Cosmetici tomadora</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Autorizado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -11433,266 +11433,270 @@
       </c>
       <c r="K5" s="11" t="n"/>
       <c r="L5" s="11" t="n">
-        <v>106</v>
+        <v>172.64</v>
       </c>
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n">
-        <v>12.27</v>
+        <v>19.87</v>
       </c>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>8936/33039048000162</t>
+          <t>8953/33039048000162</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
+          <t>CT-e cancelado - status "Cancelamento" no relatório</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>41260900428307002301570010020434981020434985</t>
+          <t>41260944914992003820570030046839841046839848</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>2043500</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="14" t="n">
+        <v>4687986</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>46268</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>RODONAVES TRANSPORTES E ENCOMENDAS LTDA</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>44914992003820</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>PR-SP</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n">
+        <v>172.64</v>
+      </c>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>8953/33039048000162</t>
+        </is>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>41260944914992003820570030046879861046879869</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>5597996</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PR-SC</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>tomador 17666331000168</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="C7" s="7" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>00428307000600</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>RS-PR</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>2564/54079636000108</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>43260900428307000600570010055979961055979961</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>3999629</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>48740351000327</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>PR-MA</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>8941/33039048000162</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020435001020435000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>2043501</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>tomador 06237330000181</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n">
-        <v>582</v>
-      </c>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>8945/33039048000162</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020435011020435016</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>4683984</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>46268</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>RODONAVES TRANSPORTES E ENCOMENDAS LTDA</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>44914992003820</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>PR-SP</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Cancelado</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n">
-        <v>172.64</v>
-      </c>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n">
-        <v>19.87</v>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>8953/33039048000162</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>CT-e cancelado - status "Cancelamento" no relatório</t>
-        </is>
-      </c>
-      <c r="Q8" s="9" t="inlineStr">
-        <is>
-          <t>41260944914992003820570030046839841046839848</t>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n">
+        <v>249.59</v>
+      </c>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>8949/33039048000162</t>
+        </is>
+      </c>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q8" s="14" t="inlineStr">
+        <is>
+          <t>41260948740351000327570000039996291544246881</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>4687986</v>
+        <v>3999630</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>RODONAVES TRANSPORTES E ENCOMENDAS LTDA</t>
+          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>44914992003820</t>
+          <t>48740351000327</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>PR-SP</t>
+          <t>PR-PA</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -11717,15 +11721,15 @@
       </c>
       <c r="K9" s="16" t="n"/>
       <c r="L9" s="16" t="n">
-        <v>172.64</v>
+        <v>264.86</v>
       </c>
       <c r="M9" s="16" t="n"/>
       <c r="N9" s="16" t="n">
-        <v>19.87</v>
+        <v>18.25</v>
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>8953/33039048000162</t>
+          <t>8946/33039048000162</t>
         </is>
       </c>
       <c r="P9" s="14" t="inlineStr">
@@ -11735,186 +11739,182 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>41260944914992003820570030046879861046879869</t>
+          <t>41260948740351000327570000039996301101761800</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>5597996</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="14" t="n">
+        <v>36425929</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>73939449000193</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>994/30415972000108</t>
+        </is>
+      </c>
+      <c r="P10" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q10" s="14" t="inlineStr">
+        <is>
+          <t>35260973939449000193579990364259291604264536</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>17817538</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>00428307000600</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>RS-PR</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="C11" s="15" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>PR-SP</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Cosmetici tomadora</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>301.49</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>301.49</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>2564/54079636000108</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>43260900428307000600570010055979961055979961</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>2052194</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>tomador 18074269000188</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>8959/33039048000162</t>
-        </is>
-      </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020521941020521946</t>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>1284/30415972000108</t>
+        </is>
+      </c>
+      <c r="P11" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010178175381661666021</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>3999629</v>
+        <v>17817833</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>48740351000327</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>PR-MA</t>
+          <t>PR-MG</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -11934,15 +11934,15 @@
       </c>
       <c r="K12" s="16" t="n"/>
       <c r="L12" s="16" t="n">
-        <v>249.59</v>
+        <v>55.55</v>
       </c>
       <c r="M12" s="16" t="n"/>
       <c r="N12" s="16" t="n">
-        <v>17.18</v>
+        <v>6.67</v>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>8949/33039048000162</t>
+          <t>1282/30415972000108</t>
         </is>
       </c>
       <c r="P12" s="14" t="inlineStr">
@@ -11952,40 +11952,40 @@
       </c>
       <c r="Q12" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000039996291544246881</t>
+          <t>41260973939449002056570010178178331686344389</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>3999630</v>
+        <v>17826831</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>48740351000327</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>PR-PA</t>
+          <t>PR-MG</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -12005,15 +12005,15 @@
       </c>
       <c r="K13" s="16" t="n"/>
       <c r="L13" s="16" t="n">
-        <v>264.86</v>
+        <v>55.85</v>
       </c>
       <c r="M13" s="16" t="n"/>
       <c r="N13" s="16" t="n">
-        <v>18.25</v>
+        <v>6.7</v>
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>8946/33039048000162</t>
+          <t>1288/30415972000108</t>
         </is>
       </c>
       <c r="P13" s="14" t="inlineStr">
@@ -12023,226 +12023,230 @@
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000039996301101761800</t>
+          <t>41260973939449002056570010178268311888893400</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>36425929</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>46276</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>73939449000193</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="A14" s="6" t="n">
+        <v>25709</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>SP-PR</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>6353</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Cosmetici tomadora</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>30338/67598292000187</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>35260903867083000290570030000257091000483871</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>4010194</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>48740351000327</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>PR-BA</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n">
-        <v>54.83</v>
-      </c>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>994/30415972000108</t>
-        </is>
-      </c>
-      <c r="P14" s="14" t="inlineStr">
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n">
+        <v>507.65</v>
+      </c>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>8974/33039048000162</t>
+        </is>
+      </c>
+      <c r="P15" s="14" t="inlineStr">
         <is>
           <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
         </is>
       </c>
-      <c r="Q14" s="14" t="inlineStr">
-        <is>
-          <t>35260973939449000193579990364259291604264536</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>2060731</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="Q15" s="14" t="inlineStr">
+        <is>
+          <t>41260948740351000327570000040101941868875491</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>2079447</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>46276</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C16" s="15" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>00428307002301</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>tomador 06237330000181</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>PR-SC</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n">
-        <v>664</v>
-      </c>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>8875/33039048000162</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020607311020607317</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>536512</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>AGEX TRANSPORTES URGENTES LTDA</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>18016343000452</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>PR-MS</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>tomador 27697083000176</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n">
-        <v>671.13</v>
-      </c>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="11" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="O16" s="9" t="inlineStr">
-        <is>
-          <t>8874/33039048000162</t>
-        </is>
-      </c>
-      <c r="P16" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q16" s="9" t="inlineStr">
-        <is>
-          <t>41260918016343000452570100005365121005163162</t>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>8987/33039048000162</t>
+        </is>
+      </c>
+      <c r="P16" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q16" s="14" t="inlineStr">
+        <is>
+          <t>41260900428307002301570010020794471020794476</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
-        <v>17817538</v>
+        <v>2081291</v>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
@@ -12250,26 +12254,26 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>TEX COURIER S.A</t>
+          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>73939449002056</t>
+          <t>00428307002301</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>PR-SP</t>
+          <t>PR-RS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -12289,15 +12293,15 @@
       </c>
       <c r="K17" s="16" t="n"/>
       <c r="L17" s="16" t="n">
-        <v>40.22</v>
+        <v>115.56</v>
       </c>
       <c r="M17" s="16" t="n"/>
       <c r="N17" s="16" t="n">
-        <v>4.83</v>
+        <v>13.41</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>1284/30415972000108</t>
+          <t>8991/33039048000162</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
@@ -12307,13 +12311,13 @@
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>41260973939449002056570010178175381661666021</t>
+          <t>41260900428307002301570010020812911020812916</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n">
-        <v>17817833</v>
+        <v>2081292</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
@@ -12321,26 +12325,26 @@
         </is>
       </c>
       <c r="C18" s="15" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>TEX COURIER S.A</t>
+          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>73939449002056</t>
+          <t>00428307002301</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>PR-MG</t>
+          <t>PR-RS</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -12360,15 +12364,15 @@
       </c>
       <c r="K18" s="16" t="n"/>
       <c r="L18" s="16" t="n">
-        <v>55.55</v>
+        <v>138.62</v>
       </c>
       <c r="M18" s="16" t="n"/>
       <c r="N18" s="16" t="n">
-        <v>6.67</v>
+        <v>16.18</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>1282/30415972000108</t>
+          <t>8996/33039048000162</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
@@ -12378,40 +12382,40 @@
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>41260973939449002056570010178178331686344389</t>
+          <t>41260900428307002301570010020812921020812921</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
-        <v>17826831</v>
+        <v>4011462</v>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>TEX COURIER S.A</t>
+          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>73939449002056</t>
+          <t>48740351000327</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>PR-MG</t>
+          <t>PR-CE</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -12431,15 +12435,15 @@
       </c>
       <c r="K19" s="16" t="n"/>
       <c r="L19" s="16" t="n">
-        <v>55.85</v>
+        <v>280.52</v>
       </c>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="n">
-        <v>6.7</v>
+        <v>19.35</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>1288/30415972000108</t>
+          <t>8983/33039048000162</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
@@ -12449,13 +12453,13 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>41260973939449002056570010178268311888893400</t>
+          <t>41260948740351000327570000040114621516701249</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>25709</v>
+        <v>25910</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
@@ -12463,7 +12467,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
@@ -12501,20 +12505,20 @@
         </is>
       </c>
       <c r="K20" s="8" t="n">
-        <v>116.03</v>
+        <v>812.3</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>116.03</v>
+        <v>812.3</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>13.92</v>
+        <v>97.48</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>13.92</v>
+        <v>97.48</v>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>30338/67598292000187</t>
+          <t>117690/59610485000188</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
@@ -12524,13 +12528,13 @@
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>35260903867083000290570030000257091000483871</t>
+          <t>35260903867083000290570030000259101000487488</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
-        <v>4010194</v>
+        <v>4014896</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
@@ -12538,7 +12542,7 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -12552,7 +12556,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>PR-BA</t>
+          <t>PR-RJ</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -12577,15 +12581,15 @@
       </c>
       <c r="K21" s="16" t="n"/>
       <c r="L21" s="16" t="n">
-        <v>507.65</v>
+        <v>240.43</v>
       </c>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="n">
-        <v>34.96</v>
+        <v>28.36</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>8974/33039048000162</t>
+          <t>8998/33039048000162</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
@@ -12595,159 +12599,155 @@
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000040101941868875491</t>
+          <t>41260948740351000327570000040148961341484558</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>9836</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="14" t="n">
+        <v>4016484</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>46289</v>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>48740351000327</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>PR-CE</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n">
+        <v>692.92</v>
+      </c>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>9010/33039048000162</t>
+        </is>
+      </c>
+      <c r="P22" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q22" s="14" t="inlineStr">
+        <is>
+          <t>41260948740351000327570000040164841595451461</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
+        <v>17890190</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>J.A. DE LUCCA TRANSPORTADORA</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>21619455000160</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>SP-SP</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>5352</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>tomador 59610485000188</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="C23" s="15" t="n">
+        <v>46289</v>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>PR-PE</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>415.94</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>415.94</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>117690/59610485000188</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>35260921619455000160570010000098361762928900</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>2079446</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>PR-SC</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>tomador 17666331000168</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>8985/33039048000162</t>
-        </is>
-      </c>
-      <c r="P23" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q23" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020794461020794460</t>
+      <c r="K23" s="16" t="n"/>
+      <c r="L23" s="16" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="16" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>1354/30415972000108</t>
+        </is>
+      </c>
+      <c r="P23" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q23" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010178901901579809677</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
-        <v>2079447</v>
+        <v>17890191</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
@@ -12755,26 +12755,26 @@
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>00428307002301</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>PR-SC</t>
+          <t>PR-SP</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
@@ -12794,15 +12794,15 @@
       </c>
       <c r="K24" s="16" t="n"/>
       <c r="L24" s="16" t="n">
-        <v>81.81999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="M24" s="16" t="n"/>
       <c r="N24" s="16" t="n">
-        <v>9.359999999999999</v>
+        <v>5.72</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>8987/33039048000162</t>
+          <t>1355/30415972000108</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
@@ -12812,84 +12812,88 @@
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>41260900428307002301570010020794471020794476</t>
+          <t>41260973939449002056570010178901911551237919</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
-        <v>2079448</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>tomador 06237330000181</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="A25" s="6" t="n">
+        <v>26411</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="11" t="n">
-        <v>502</v>
-      </c>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>8992/33039048000162</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020794481020794481</t>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>141811/62514971000107</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>35260903867083000290570030000264111000496392</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
-        <v>2081291</v>
+        <v>17896252</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
@@ -12897,26 +12901,26 @@
         </is>
       </c>
       <c r="C26" s="15" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>00428307002301</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>PR-RS</t>
+          <t>PR-SP</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
@@ -12936,15 +12940,15 @@
       </c>
       <c r="K26" s="16" t="n"/>
       <c r="L26" s="16" t="n">
-        <v>115.56</v>
+        <v>38.66</v>
       </c>
       <c r="M26" s="16" t="n"/>
       <c r="N26" s="16" t="n">
-        <v>13.41</v>
+        <v>4.64</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>8991/33039048000162</t>
+          <t>1380/30415972000108</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
@@ -12954,13 +12958,13 @@
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>41260900428307002301570010020812911020812916</t>
+          <t>41260973939449002056570010178962521387579519</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>2081292</v>
+        <v>17901568</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
@@ -12968,26 +12972,26 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>00428307002301</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>PR-RS</t>
+          <t>PR-SC</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -13007,15 +13011,15 @@
       </c>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="16" t="n">
-        <v>138.62</v>
+        <v>20.82</v>
       </c>
       <c r="M27" s="16" t="n"/>
       <c r="N27" s="16" t="n">
-        <v>16.18</v>
+        <v>2.5</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>8996/33039048000162</t>
+          <t>1396/30415972000108</t>
         </is>
       </c>
       <c r="P27" s="14" t="inlineStr">
@@ -13025,40 +13029,40 @@
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>41260900428307002301570010020812921020812921</t>
+          <t>41260973939449002056570010179015681681992936</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
-        <v>4011462</v>
+        <v>17901582</v>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>48740351000327</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>PR-CE</t>
+          <t>PR-SP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -13078,15 +13082,15 @@
       </c>
       <c r="K28" s="16" t="n"/>
       <c r="L28" s="16" t="n">
-        <v>280.52</v>
+        <v>51.09</v>
       </c>
       <c r="M28" s="16" t="n"/>
       <c r="N28" s="16" t="n">
-        <v>19.35</v>
+        <v>6.13</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>8983/33039048000162</t>
+          <t>1397/30415972000108</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
@@ -13096,624 +13100,608 @@
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000040114621516701249</t>
+          <t>41260973939449002056570010179015821611093770</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>4011463</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>46286</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>48740351000327</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>PR-RJ</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="A29" s="14" t="n">
+        <v>17901583</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>PR-RS</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>1392/30415972000108</t>
+        </is>
+      </c>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q29" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179015831130565736</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>17901596</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>PR-SP</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>1379/30415972000108</t>
+        </is>
+      </c>
+      <c r="P30" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q30" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179015961538845580</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>17901597</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>PR-MG</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="16" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>1390/30415972000108</t>
+        </is>
+      </c>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q31" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179015971354021905</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>17901624</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>PR-DF</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>1377/30415972000108</t>
+        </is>
+      </c>
+      <c r="P32" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q32" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179016241104385135</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>2095396</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>00428307002301</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>PR-RS</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>6352</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>tomador 05268903000171</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n">
-        <v>110.94</v>
-      </c>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>8994/33039048000162</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>41260948740351000327570000040114631964587846</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>1106604</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="K33" s="16" t="n"/>
+      <c r="L33" s="16" t="n">
+        <v>146.44</v>
+      </c>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="16" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>9015/33039048000162</t>
+        </is>
+      </c>
+      <c r="P33" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q33" s="14" t="inlineStr">
+        <is>
+          <t>41260900428307002301570010020953961020953963</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>17915091</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>46287</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TRANSAL TRANSPORTADORA SALVAN LTDA</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>00214121000217</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="C34" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>PR-RS</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="n"/>
+      <c r="L34" s="16" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="16" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>1407/30415972000108</t>
+        </is>
+      </c>
+      <c r="P34" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q34" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179150911045858097</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>2098798</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>00428307002301</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>PR-RS</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>6352</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>tomador 49698723003110</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Cosmetici tomadora</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>170.66</v>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>170.66</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="N30" s="8" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>275966/49698723003110</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>35260900214121000217570010011066041079491008</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>25910</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>46287</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>03867083000290</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="n"/>
+      <c r="L35" s="16" t="n">
+        <v>445.46</v>
+      </c>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="16" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>9017/33039048000162</t>
+        </is>
+      </c>
+      <c r="P35" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>41260900428307002301570010020987981020987981</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>17924737</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>TEX COURIER S.A</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>73939449002056</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>PR-MG</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>6353</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>Cosmetici tomadora</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="n">
-        <v>812.3</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>812.3</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>97.48</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>97.48</v>
-      </c>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>117690/59610485000188</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>35260903867083000290570030000259101000487488</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>11891</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>CLARO TRANSPORTES E LOGISTICA</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>03812091001200</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>6357</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>tomador 66229009000187</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>258.4</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>258.4</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>8112/34970658000148</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>35260903812091001200570010000118911002325123</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
-        <v>11892</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>CLARO TRANSPORTES E LOGISTICA</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>03812091001200</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>6357</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>tomador 66229009000187</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>301.68</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>301.68</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>8099/39237959000180</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>35260903812091001200570010000118921002325139</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n">
-        <v>2085389</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>tomador 32232914000174</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="K34" s="11" t="n"/>
-      <c r="L34" s="11" t="n">
-        <v>101</v>
-      </c>
-      <c r="M34" s="11" t="n"/>
-      <c r="N34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="9" t="inlineStr">
-        <is>
-          <t>9007/33039048000162</t>
-        </is>
-      </c>
-      <c r="P34" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020853891020853898</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>2085390</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>tomador 06237330000181</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n">
-        <v>472</v>
-      </c>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="9" t="inlineStr">
-        <is>
-          <t>9002/33039048000162</t>
-        </is>
-      </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020853901020853902</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n">
-        <v>538070</v>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>AGEX TRANSPORTES URGENTES LTDA</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>18016343000452</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>PR-MS</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>tomador 27697083000176</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="n"/>
-      <c r="L36" s="11" t="n">
-        <v>1878.72</v>
-      </c>
-      <c r="M36" s="11" t="n"/>
-      <c r="N36" s="11" t="n">
-        <v>125.8</v>
-      </c>
-      <c r="O36" s="9" t="inlineStr">
-        <is>
-          <t>9004/33039048000162</t>
-        </is>
-      </c>
-      <c r="P36" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q36" s="9" t="inlineStr">
-        <is>
-          <t>41260918016343000452570100005380701005234499</t>
+      <c r="K36" s="16" t="n"/>
+      <c r="L36" s="16" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>1442/30415972000108</t>
+        </is>
+      </c>
+      <c r="P36" s="14" t="inlineStr">
+        <is>
+          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
+        </is>
+      </c>
+      <c r="Q36" s="14" t="inlineStr">
+        <is>
+          <t>41260973939449002056570010179247371948650364</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
-        <v>4014896</v>
+        <v>17924803</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>48740351000327</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>PR-RJ</t>
+          <t>PR-MG</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -13733,15 +13721,15 @@
       </c>
       <c r="K37" s="16" t="n"/>
       <c r="L37" s="16" t="n">
-        <v>240.43</v>
+        <v>28.56</v>
       </c>
       <c r="M37" s="16" t="n"/>
       <c r="N37" s="16" t="n">
-        <v>28.36</v>
+        <v>3.43</v>
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>8998/33039048000162</t>
+          <t>1438/30415972000108</t>
         </is>
       </c>
       <c r="P37" s="14" t="inlineStr">
@@ -13751,40 +13739,40 @@
       </c>
       <c r="Q37" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000040148961341484558</t>
+          <t>41260973939449002056570010179248031905329170</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
-        <v>4016484</v>
+        <v>17924811</v>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" s="15" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>BRASPRESS TRANSPORTES URGENTES LTDA</t>
+          <t>TEX COURIER S.A</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>48740351000327</t>
+          <t>73939449002056</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>PR-CE</t>
+          <t>PR-RS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
@@ -13804,15 +13792,15 @@
       </c>
       <c r="K38" s="16" t="n"/>
       <c r="L38" s="16" t="n">
-        <v>692.92</v>
+        <v>24.74</v>
       </c>
       <c r="M38" s="16" t="n"/>
       <c r="N38" s="16" t="n">
-        <v>47.93</v>
+        <v>2.97</v>
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>9010/33039048000162</t>
+          <t>1409/30415972000108</t>
         </is>
       </c>
       <c r="P38" s="14" t="inlineStr">
@@ -13822,1688 +13810,110 @@
       </c>
       <c r="Q38" s="14" t="inlineStr">
         <is>
-          <t>41260948740351000327570000040164841595451461</t>
+          <t>41260973939449002056570010179248111268602370</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n">
-        <v>17890190</v>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>46289</v>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>PR-PE</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="A39" s="6" t="n">
+        <v>26730</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>6353</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Cosmetici tomadora</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n">
-        <v>221.5</v>
-      </c>
-      <c r="M39" s="16" t="n"/>
-      <c r="N39" s="16" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="O39" s="14" t="inlineStr">
-        <is>
-          <t>1354/30415972000108</t>
-        </is>
-      </c>
-      <c r="P39" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q39" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010178901901579809677</t>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>188.49</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>188.49</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>19303/58309709000820</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>35260903867083000290570030000267301000504028</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n">
-        <v>17890191</v>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>46289</v>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>PR-SP</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="M40" s="16" t="n"/>
-      <c r="N40" s="16" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="O40" s="14" t="inlineStr">
-        <is>
-          <t>1355/30415972000108</t>
-        </is>
-      </c>
-      <c r="P40" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q40" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010178901911551237919</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>26411</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>03867083000290</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>126.02</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>126.02</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="O41" s="6" t="inlineStr">
-        <is>
-          <t>141811/62514971000107</t>
-        </is>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>35260903867083000290570030000264111000496392</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="n">
-        <v>17896252</v>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>PR-SP</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n">
-        <v>38.66</v>
-      </c>
-      <c r="M42" s="16" t="n"/>
-      <c r="N42" s="16" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="O42" s="14" t="inlineStr">
-        <is>
-          <t>1380/30415972000108</t>
-        </is>
-      </c>
-      <c r="P42" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q42" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010178962521387579519</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="n">
-        <v>17901568</v>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>PR-SC</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n">
-        <v>20.82</v>
-      </c>
-      <c r="M43" s="16" t="n"/>
-      <c r="N43" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O43" s="14" t="inlineStr">
-        <is>
-          <t>1396/30415972000108</t>
-        </is>
-      </c>
-      <c r="P43" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q43" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179015681681992936</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="n">
-        <v>17901582</v>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>PR-SP</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="M44" s="16" t="n"/>
-      <c r="N44" s="16" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="O44" s="14" t="inlineStr">
-        <is>
-          <t>1397/30415972000108</t>
-        </is>
-      </c>
-      <c r="P44" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q44" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179015821611093770</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="n">
-        <v>17901583</v>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>PR-RS</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="16" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="M45" s="16" t="n"/>
-      <c r="N45" s="16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O45" s="14" t="inlineStr">
-        <is>
-          <t>1392/30415972000108</t>
-        </is>
-      </c>
-      <c r="P45" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q45" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179015831130565736</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="n">
-        <v>17901596</v>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>PR-SP</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="16" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="M46" s="16" t="n"/>
-      <c r="N46" s="16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O46" s="14" t="inlineStr">
-        <is>
-          <t>1379/30415972000108</t>
-        </is>
-      </c>
-      <c r="P46" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q46" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179015961538845580</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="n">
-        <v>17901597</v>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>PR-MG</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="16" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="M47" s="16" t="n"/>
-      <c r="N47" s="16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="O47" s="14" t="inlineStr">
-        <is>
-          <t>1390/30415972000108</t>
-        </is>
-      </c>
-      <c r="P47" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q47" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179015971354021905</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="n">
-        <v>17901624</v>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>PR-DF</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J48" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="16" t="n">
-        <v>28.31</v>
-      </c>
-      <c r="M48" s="16" t="n"/>
-      <c r="N48" s="16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O48" s="14" t="inlineStr">
-        <is>
-          <t>1377/30415972000108</t>
-        </is>
-      </c>
-      <c r="P48" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q48" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179016241104385135</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="n">
-        <v>2095396</v>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="n">
-        <v>46293</v>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>PR-RS</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="16" t="n">
-        <v>146.44</v>
-      </c>
-      <c r="M49" s="16" t="n"/>
-      <c r="N49" s="16" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="O49" s="14" t="inlineStr">
-        <is>
-          <t>9015/33039048000162</t>
-        </is>
-      </c>
-      <c r="P49" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020953961020953963</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n">
-        <v>6152</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>46293</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TOPCON EXPRESS TRANSPORTE E LOGISTICA LTDA</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>14222849000114</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>tomador 03812091000239</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>8099/39237959000180</t>
-        </is>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>41260914222849000114570010000061521000069767</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n">
-        <v>6153</v>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>46293</v>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TOPCON EXPRESS TRANSPORTE E LOGISTICA LTDA</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>14222849000114</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>tomador 03812091000239</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="L51" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>8112/34970658000148</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>41260914222849000114570010000061531000069772</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="n">
-        <v>17915091</v>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="n">
-        <v>46293</v>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>PR-RS</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J52" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="16" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="M52" s="16" t="n"/>
-      <c r="N52" s="16" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="O52" s="14" t="inlineStr">
-        <is>
-          <t>1407/30415972000108</t>
-        </is>
-      </c>
-      <c r="P52" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q52" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179150911045858097</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="n">
-        <v>2098798</v>
-      </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="n">
-        <v>46294</v>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>PR-RS</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>6352</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J53" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="16" t="n">
-        <v>445.46</v>
-      </c>
-      <c r="M53" s="16" t="n"/>
-      <c r="N53" s="16" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="O53" s="14" t="inlineStr">
-        <is>
-          <t>9017/33039048000162</t>
-        </is>
-      </c>
-      <c r="P53" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q53" s="14" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010020987981020987981</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="n">
-        <v>17924737</v>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="n">
-        <v>46294</v>
-      </c>
-      <c r="D54" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>PR-MG</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J54" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n">
-        <v>55.04</v>
-      </c>
-      <c r="M54" s="16" t="n"/>
-      <c r="N54" s="16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O54" s="14" t="inlineStr">
-        <is>
-          <t>1442/30415972000108</t>
-        </is>
-      </c>
-      <c r="P54" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q54" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179247371948650364</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="n">
-        <v>17924803</v>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="n">
-        <v>46294</v>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>PR-MG</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J55" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="16" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="M55" s="16" t="n"/>
-      <c r="N55" s="16" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="O55" s="14" t="inlineStr">
-        <is>
-          <t>1438/30415972000108</t>
-        </is>
-      </c>
-      <c r="P55" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q55" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179248031905329170</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="n">
-        <v>17924811</v>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="n">
-        <v>46294</v>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>TEX COURIER S.A</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>73939449002056</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>PR-RS</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J56" s="14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="M56" s="16" t="n"/>
-      <c r="N56" s="16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O56" s="14" t="inlineStr">
-        <is>
-          <t>1409/30415972000108</t>
-        </is>
-      </c>
-      <c r="P56" s="14" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (Cosmetici tomadora - pedir o XML)</t>
-        </is>
-      </c>
-      <c r="Q56" s="14" t="inlineStr">
-        <is>
-          <t>41260973939449002056570010179248111268602370</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n">
-        <v>26730</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>03867083000290</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>SP-PR</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>Cosmetici tomadora</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="n">
-        <v>188.49</v>
-      </c>
-      <c r="L57" s="8" t="n">
-        <v>188.49</v>
-      </c>
-      <c r="M57" s="8" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="N57" s="8" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>19303/58309709000820</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>35260903867083000290570030000267301000504028</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="n">
-        <v>7245</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>TRANSPORTADORA SABIA DE MARILI</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>59512962000172</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>MG-SP</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>tomador 58309709000820</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="n">
-        <v>499.42</v>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>499.42</v>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="inlineStr">
-        <is>
-          <t>19303/58309709000820</t>
-        </is>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>35260959512962000172570020000072451001308896</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n">
-        <v>2101677</v>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>PR-SC</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>tomador 17666331000168</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K59" s="11" t="n"/>
-      <c r="L59" s="11" t="n">
-        <v>112</v>
-      </c>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="O59" s="9" t="inlineStr">
-        <is>
-          <t>9027/33039048000162</t>
-        </is>
-      </c>
-      <c r="P59" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q59" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010021016771021016770</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n">
-        <v>2101678</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>CURITIBA - EXPRESSO SAO MIGUEL S/A</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>00428307002301</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>PR-PR</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>tomador 06237330000181</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="n"/>
-      <c r="L60" s="11" t="n">
-        <v>286</v>
-      </c>
-      <c r="M60" s="11" t="n"/>
-      <c r="N60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="9" t="inlineStr">
-        <is>
-          <t>9023/33039048000162</t>
-        </is>
-      </c>
-      <c r="P60" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q60" s="9" t="inlineStr">
-        <is>
-          <t>41260900428307002301570010021016781021016785</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="n">
-        <v>539506</v>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>AGEX TRANSPORTES URGENTES LTDA</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>18016343000452</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>PR-MS</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>tomador 27697083000176</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Autorizado</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K61" s="11" t="n"/>
-      <c r="L61" s="11" t="n">
-        <v>1212.45</v>
-      </c>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n">
-        <v>81.61</v>
-      </c>
-      <c r="O61" s="9" t="inlineStr">
-        <is>
-          <t>9025/33039048000162</t>
-        </is>
-      </c>
-      <c r="P61" s="9" t="inlineStr">
-        <is>
-          <t>Sem XML na pasta (tomador é outra empresa)</t>
-        </is>
-      </c>
-      <c r="Q61" s="9" t="inlineStr">
-        <is>
-          <t>41260918016343000452570100005395061005299478</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K62" s="13">
-        <f>SUM(K5:K61)</f>
+      <c r="K40" s="13">
+        <f>SUM(K5:K39)</f>
         <v/>
       </c>
-      <c r="L62" s="13">
-        <f>SUM(L5:L61)</f>
+      <c r="L40" s="13">
+        <f>SUM(L5:L39)</f>
         <v/>
       </c>
-      <c r="M62" s="13">
-        <f>SUM(M5:M61)</f>
+      <c r="M40" s="13">
+        <f>SUM(M5:M39)</f>
         <v/>
       </c>
-      <c r="N62" s="13">
-        <f>SUM(N5:N61)</f>
+      <c r="N40" s="13">
+        <f>SUM(N5:N39)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q61"/>
+  <autoFilter ref="A4:Q39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
